--- a/modules/log/Ревизор - Жамшид.xlsx
+++ b/modules/log/Ревизор - Жамшид.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N78"/>
+  <dimension ref="A1:N158"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3834,11 +3834,3531 @@
         <v>59</v>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B79" t="str">
+        <v>19035</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Исабеков</v>
+      </c>
+      <c r="D79" t="str">
+        <v>Маликова</v>
+      </c>
+      <c r="E79" t="str">
+        <v>32</v>
+      </c>
+      <c r="F79" t="str">
+        <v>44135</v>
+      </c>
+      <c r="G79" t="str">
+        <v>670</v>
+      </c>
+      <c r="H79" t="str">
+        <v>794</v>
+      </c>
+      <c r="I79" t="str">
+        <v>124</v>
+      </c>
+      <c r="J79" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K79" t="str">
+        <v>6</v>
+      </c>
+      <c r="L79" t="str">
+        <v>20</v>
+      </c>
+      <c r="M79" t="str">
+        <v>12</v>
+      </c>
+      <c r="N79" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B80" t="str">
+        <v>19024</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Тукибаева Алиша</v>
+      </c>
+      <c r="D80" t="str">
+        <v>Маликова</v>
+      </c>
+      <c r="E80" t="str">
+        <v>28</v>
+      </c>
+      <c r="F80" t="str">
+        <v>77964</v>
+      </c>
+      <c r="G80" t="str">
+        <v>595</v>
+      </c>
+      <c r="H80" t="str">
+        <v>649</v>
+      </c>
+      <c r="I80" t="str">
+        <v>54</v>
+      </c>
+      <c r="J80" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K80" t="str">
+        <v>6</v>
+      </c>
+      <c r="L80" t="str">
+        <v>20</v>
+      </c>
+      <c r="M80" t="str">
+        <v>12</v>
+      </c>
+      <c r="N80" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B81" t="str">
+        <v>23336</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Самал кафе</v>
+      </c>
+      <c r="D81" t="str">
+        <v>Караб.шоссе</v>
+      </c>
+      <c r="E81" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F81" t="str">
+        <v>50515</v>
+      </c>
+      <c r="G81" t="str">
+        <v>1323</v>
+      </c>
+      <c r="H81" t="str">
+        <v>1384</v>
+      </c>
+      <c r="I81" t="str">
+        <v>61</v>
+      </c>
+      <c r="J81" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K81" t="str">
+        <v>7</v>
+      </c>
+      <c r="L81" t="str">
+        <v>3</v>
+      </c>
+      <c r="M81" t="str">
+        <v>22</v>
+      </c>
+      <c r="N81" t="str">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B82" t="str">
+        <v>23916</v>
+      </c>
+      <c r="C82" t="str">
+        <v>ИП Турашбеков</v>
+      </c>
+      <c r="D82" t="str">
+        <v>Караб.шоссе</v>
+      </c>
+      <c r="E82" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F82" t="str">
+        <v>55869</v>
+      </c>
+      <c r="G82" t="str">
+        <v>1555</v>
+      </c>
+      <c r="H82" t="str">
+        <v>1600</v>
+      </c>
+      <c r="I82" t="str">
+        <v>45</v>
+      </c>
+      <c r="J82" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K82" t="str">
+        <v>7</v>
+      </c>
+      <c r="L82" t="str">
+        <v>3</v>
+      </c>
+      <c r="M82" t="str">
+        <v>22</v>
+      </c>
+      <c r="N82" t="str">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B83" t="str">
+        <v>22641</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Юмакс / ИП</v>
+      </c>
+      <c r="D83" t="str">
+        <v>Караб.шоссе</v>
+      </c>
+      <c r="E83" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F83" t="str">
+        <v>64349</v>
+      </c>
+      <c r="G83" t="str">
+        <v>2226</v>
+      </c>
+      <c r="H83" t="str">
+        <v>2246</v>
+      </c>
+      <c r="I83" t="str">
+        <v>20</v>
+      </c>
+      <c r="J83" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K83" t="str">
+        <v>7</v>
+      </c>
+      <c r="L83" t="str">
+        <v>3</v>
+      </c>
+      <c r="M83" t="str">
+        <v>22</v>
+      </c>
+      <c r="N83" t="str">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B84" t="str">
+        <v>22645</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Кафе "Султан"</v>
+      </c>
+      <c r="D84" t="str">
+        <v>Караб.шоссе</v>
+      </c>
+      <c r="E84" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F84" t="str">
+        <v>80515</v>
+      </c>
+      <c r="G84" t="str">
+        <v>183</v>
+      </c>
+      <c r="H84" t="str">
+        <v>220</v>
+      </c>
+      <c r="I84" t="str">
+        <v>37</v>
+      </c>
+      <c r="J84" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K84" t="str">
+        <v>7</v>
+      </c>
+      <c r="L84" t="str">
+        <v>3</v>
+      </c>
+      <c r="M84" t="str">
+        <v>22</v>
+      </c>
+      <c r="N84" t="str">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B85" t="str">
+        <v>2458</v>
+      </c>
+      <c r="C85" t="str">
+        <v>ТНП Бурбеков (Юсуф)</v>
+      </c>
+      <c r="D85" t="str">
+        <v>Организация</v>
+      </c>
+      <c r="E85" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F85" t="str">
+        <v>77659</v>
+      </c>
+      <c r="G85" t="str">
+        <v>500</v>
+      </c>
+      <c r="H85" t="str">
+        <v>510</v>
+      </c>
+      <c r="I85" t="str">
+        <v>10</v>
+      </c>
+      <c r="J85" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K85" t="str">
+        <v>7</v>
+      </c>
+      <c r="L85" t="str">
+        <v>3</v>
+      </c>
+      <c r="M85" t="str">
+        <v>22</v>
+      </c>
+      <c r="N85" t="str">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B86" t="str">
+        <v>2445</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Кафе "Жансая"</v>
+      </c>
+      <c r="D86" t="str">
+        <v>Организация</v>
+      </c>
+      <c r="E86" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F86" t="str">
+        <v>61342</v>
+      </c>
+      <c r="G86" t="str">
+        <v>911</v>
+      </c>
+      <c r="H86" t="str">
+        <v>920</v>
+      </c>
+      <c r="I86" t="str">
+        <v>9</v>
+      </c>
+      <c r="J86" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K86" t="str">
+        <v>7</v>
+      </c>
+      <c r="L86" t="str">
+        <v>3</v>
+      </c>
+      <c r="M86" t="str">
+        <v>22</v>
+      </c>
+      <c r="N86" t="str">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B87" t="str">
+        <v>2444</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Аптека "Даур"</v>
+      </c>
+      <c r="D87" t="str">
+        <v>Организация</v>
+      </c>
+      <c r="E87" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F87" t="str">
+        <v>55815</v>
+      </c>
+      <c r="G87" t="str">
+        <v>171</v>
+      </c>
+      <c r="H87" t="str">
+        <v>175</v>
+      </c>
+      <c r="I87" t="str">
+        <v>4</v>
+      </c>
+      <c r="J87" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K87" t="str">
+        <v>7</v>
+      </c>
+      <c r="L87" t="str">
+        <v>3</v>
+      </c>
+      <c r="M87" t="str">
+        <v>22</v>
+      </c>
+      <c r="N87" t="str">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B88" t="str">
+        <v>33619</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Мойка 911</v>
+      </c>
+      <c r="D88" t="str">
+        <v>Сураншы Батыра</v>
+      </c>
+      <c r="E88" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F88" t="str">
+        <v>48096</v>
+      </c>
+      <c r="G88" t="str">
+        <v>9432</v>
+      </c>
+      <c r="H88" t="str">
+        <v>9468</v>
+      </c>
+      <c r="I88" t="str">
+        <v>36</v>
+      </c>
+      <c r="J88" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K88" t="str">
+        <v>7</v>
+      </c>
+      <c r="L88" t="str">
+        <v>3</v>
+      </c>
+      <c r="M88" t="str">
+        <v>22</v>
+      </c>
+      <c r="N88" t="str">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B89" t="str">
+        <v>2428</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Стоматология</v>
+      </c>
+      <c r="D89" t="str">
+        <v>Сураншы Батыра 1</v>
+      </c>
+      <c r="E89" t="str">
+        <v>2-3</v>
+      </c>
+      <c r="F89" t="str">
+        <v>34972</v>
+      </c>
+      <c r="G89" t="str">
+        <v>501</v>
+      </c>
+      <c r="H89" t="str">
+        <v>510</v>
+      </c>
+      <c r="I89" t="str">
+        <v>9</v>
+      </c>
+      <c r="J89" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K89" t="str">
+        <v>7</v>
+      </c>
+      <c r="L89" t="str">
+        <v>3</v>
+      </c>
+      <c r="M89" t="str">
+        <v>22</v>
+      </c>
+      <c r="N89" t="str">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B90" t="str">
+        <v>35477</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Ип Али Даряб</v>
+      </c>
+      <c r="D90" t="str">
+        <v>Чкалова</v>
+      </c>
+      <c r="E90" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F90" t="str">
+        <v>81883</v>
+      </c>
+      <c r="G90" t="str">
+        <v>84</v>
+      </c>
+      <c r="H90" t="str">
+        <v>100</v>
+      </c>
+      <c r="I90" t="str">
+        <v>16</v>
+      </c>
+      <c r="J90" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K90" t="str">
+        <v>7</v>
+      </c>
+      <c r="L90" t="str">
+        <v>3</v>
+      </c>
+      <c r="M90" t="str">
+        <v>22</v>
+      </c>
+      <c r="N90" t="str">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B91" t="str">
+        <v>27688</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Адахамова Марифат</v>
+      </c>
+      <c r="D91" t="str">
+        <v>Шаймердинова</v>
+      </c>
+      <c r="E91" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F91" t="str">
+        <v>61373</v>
+      </c>
+      <c r="G91" t="str">
+        <v>236</v>
+      </c>
+      <c r="H91" t="str">
+        <v>240</v>
+      </c>
+      <c r="I91" t="str">
+        <v>4</v>
+      </c>
+      <c r="J91" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K91" t="str">
+        <v>7</v>
+      </c>
+      <c r="L91" t="str">
+        <v>3</v>
+      </c>
+      <c r="M91" t="str">
+        <v>22</v>
+      </c>
+      <c r="N91" t="str">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B92" t="str">
+        <v>35377</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Сайдазимов Вахид</v>
+      </c>
+      <c r="D92" t="str">
+        <v>Курбенова</v>
+      </c>
+      <c r="E92" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F92" t="str">
+        <v>55148</v>
+      </c>
+      <c r="G92" t="str">
+        <v>515</v>
+      </c>
+      <c r="H92" t="str">
+        <v>552</v>
+      </c>
+      <c r="I92" t="str">
+        <v>37</v>
+      </c>
+      <c r="J92" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K92" t="str">
+        <v>8</v>
+      </c>
+      <c r="L92" t="str">
+        <v>25</v>
+      </c>
+      <c r="M92" t="str">
+        <v>17</v>
+      </c>
+      <c r="N92" t="str">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B93" t="str">
+        <v>35380</v>
+      </c>
+      <c r="C93" t="str">
+        <v>Ермекбаева Алия</v>
+      </c>
+      <c r="D93" t="str">
+        <v>Курбенова</v>
+      </c>
+      <c r="E93" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F93" t="str">
+        <v>81506</v>
+      </c>
+      <c r="G93" t="str">
+        <v>285</v>
+      </c>
+      <c r="H93" t="str">
+        <v>331</v>
+      </c>
+      <c r="I93" t="str">
+        <v>46</v>
+      </c>
+      <c r="J93" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K93" t="str">
+        <v>8</v>
+      </c>
+      <c r="L93" t="str">
+        <v>25</v>
+      </c>
+      <c r="M93" t="str">
+        <v>17</v>
+      </c>
+      <c r="N93" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B94" t="str">
+        <v>35408</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Мирахметова Клара</v>
+      </c>
+      <c r="D94" t="str">
+        <v>Курбенова</v>
+      </c>
+      <c r="E94" t="str">
+        <v>10/3</v>
+      </c>
+      <c r="F94" t="str">
+        <v>77539</v>
+      </c>
+      <c r="G94" t="str">
+        <v>775</v>
+      </c>
+      <c r="H94" t="str">
+        <v>859</v>
+      </c>
+      <c r="I94" t="str">
+        <v>84</v>
+      </c>
+      <c r="J94" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K94" t="str">
+        <v>9</v>
+      </c>
+      <c r="L94" t="str">
+        <v>3</v>
+      </c>
+      <c r="M94" t="str">
+        <v>22</v>
+      </c>
+      <c r="N94" t="str">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B95" t="str">
+        <v>8372</v>
+      </c>
+      <c r="C95" t="str">
+        <v>Абдирахманов Л</v>
+      </c>
+      <c r="D95" t="str">
+        <v>А.Навоий (Колкент)</v>
+      </c>
+      <c r="E95" t="str">
+        <v>44к/110</v>
+      </c>
+      <c r="F95" t="str">
+        <v>66773</v>
+      </c>
+      <c r="G95" t="str">
+        <v>247</v>
+      </c>
+      <c r="H95" t="str">
+        <v>305</v>
+      </c>
+      <c r="I95" t="str">
+        <v>58</v>
+      </c>
+      <c r="J95" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K95" t="str">
+        <v>9</v>
+      </c>
+      <c r="L95" t="str">
+        <v>10</v>
+      </c>
+      <c r="M95" t="str">
+        <v>13</v>
+      </c>
+      <c r="N95" t="str">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B96" t="str">
+        <v>8376</v>
+      </c>
+      <c r="C96" t="str">
+        <v>Усманов У</v>
+      </c>
+      <c r="D96" t="str">
+        <v>А.Навоий (Колкент)</v>
+      </c>
+      <c r="E96" t="str">
+        <v>44к/114</v>
+      </c>
+      <c r="F96" t="str">
+        <v>66795</v>
+      </c>
+      <c r="G96" t="str">
+        <v>579</v>
+      </c>
+      <c r="H96" t="str">
+        <v>674</v>
+      </c>
+      <c r="I96" t="str">
+        <v>95</v>
+      </c>
+      <c r="J96" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K96" t="str">
+        <v>9</v>
+      </c>
+      <c r="L96" t="str">
+        <v>10</v>
+      </c>
+      <c r="M96" t="str">
+        <v>13</v>
+      </c>
+      <c r="N96" t="str">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B97" t="str">
+        <v>14186</v>
+      </c>
+      <c r="C97" t="str">
+        <v>Абдурахманов М</v>
+      </c>
+      <c r="D97" t="str">
+        <v>А.Навоий (Колкент)</v>
+      </c>
+      <c r="E97" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F97" t="str">
+        <v>81654</v>
+      </c>
+      <c r="G97" t="str">
+        <v>138</v>
+      </c>
+      <c r="H97" t="str">
+        <v>208</v>
+      </c>
+      <c r="I97" t="str">
+        <v>70</v>
+      </c>
+      <c r="J97" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K97" t="str">
+        <v>9</v>
+      </c>
+      <c r="L97" t="str">
+        <v>10</v>
+      </c>
+      <c r="M97" t="str">
+        <v>13</v>
+      </c>
+      <c r="N97" t="str">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B98" t="str">
+        <v>8373</v>
+      </c>
+      <c r="C98" t="str">
+        <v>Абдирахманов Р</v>
+      </c>
+      <c r="D98" t="str">
+        <v>А.Навоий (Колкент)</v>
+      </c>
+      <c r="E98" t="str">
+        <v>44к/111</v>
+      </c>
+      <c r="F98" t="str">
+        <v>66772</v>
+      </c>
+      <c r="G98" t="str">
+        <v>665</v>
+      </c>
+      <c r="H98" t="str">
+        <v>797</v>
+      </c>
+      <c r="I98" t="str">
+        <v>132</v>
+      </c>
+      <c r="J98" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K98" t="str">
+        <v>9</v>
+      </c>
+      <c r="L98" t="str">
+        <v>10</v>
+      </c>
+      <c r="M98" t="str">
+        <v>13</v>
+      </c>
+      <c r="N98" t="str">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B99" t="str">
+        <v>8375</v>
+      </c>
+      <c r="C99" t="str">
+        <v>Юлдашниязов С</v>
+      </c>
+      <c r="D99" t="str">
+        <v>А.Навоий (Колкент)</v>
+      </c>
+      <c r="E99" t="str">
+        <v>44к/113</v>
+      </c>
+      <c r="F99" t="str">
+        <v>66105</v>
+      </c>
+      <c r="G99" t="str">
+        <v>1457</v>
+      </c>
+      <c r="H99" t="str">
+        <v>1560</v>
+      </c>
+      <c r="I99" t="str">
+        <v>103</v>
+      </c>
+      <c r="J99" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K99" t="str">
+        <v>9</v>
+      </c>
+      <c r="L99" t="str">
+        <v>10</v>
+      </c>
+      <c r="M99" t="str">
+        <v>13</v>
+      </c>
+      <c r="N99" t="str">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B100" t="str">
+        <v>8370</v>
+      </c>
+      <c r="C100" t="str">
+        <v>Рузимурадов Э</v>
+      </c>
+      <c r="D100" t="str">
+        <v>А.Навоий (Колкент)</v>
+      </c>
+      <c r="E100" t="str">
+        <v>43к/109</v>
+      </c>
+      <c r="F100" t="str">
+        <v>50067</v>
+      </c>
+      <c r="G100" t="str">
+        <v>2624</v>
+      </c>
+      <c r="H100" t="str">
+        <v>2727</v>
+      </c>
+      <c r="I100" t="str">
+        <v>103</v>
+      </c>
+      <c r="J100" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K100" t="str">
+        <v>9</v>
+      </c>
+      <c r="L100" t="str">
+        <v>10</v>
+      </c>
+      <c r="M100" t="str">
+        <v>13</v>
+      </c>
+      <c r="N100" t="str">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B101" t="str">
+        <v>8365</v>
+      </c>
+      <c r="C101" t="str">
+        <v>Ешметов Х</v>
+      </c>
+      <c r="D101" t="str">
+        <v>А.Навоий (Колкент)</v>
+      </c>
+      <c r="E101" t="str">
+        <v>43к/103</v>
+      </c>
+      <c r="F101" t="str">
+        <v>60348</v>
+      </c>
+      <c r="G101" t="str">
+        <v>606</v>
+      </c>
+      <c r="H101" t="str">
+        <v>612</v>
+      </c>
+      <c r="I101" t="str">
+        <v>6</v>
+      </c>
+      <c r="J101" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K101" t="str">
+        <v>9</v>
+      </c>
+      <c r="L101" t="str">
+        <v>10</v>
+      </c>
+      <c r="M101" t="str">
+        <v>13</v>
+      </c>
+      <c r="N101" t="str">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B102" t="str">
+        <v>17833</v>
+      </c>
+      <c r="C102" t="str">
+        <v>Абдуллаева Зубайда</v>
+      </c>
+      <c r="D102" t="str">
+        <v>Шаймердинова</v>
+      </c>
+      <c r="E102" t="str">
+        <v>66</v>
+      </c>
+      <c r="F102" t="str">
+        <v>75003</v>
+      </c>
+      <c r="G102" t="str">
+        <v>324</v>
+      </c>
+      <c r="H102" t="str">
+        <v>413</v>
+      </c>
+      <c r="I102" t="str">
+        <v>89</v>
+      </c>
+      <c r="J102" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K102" t="str">
+        <v>9</v>
+      </c>
+      <c r="L102" t="str">
+        <v>12</v>
+      </c>
+      <c r="M102" t="str">
+        <v>15</v>
+      </c>
+      <c r="N102" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B103" t="str">
+        <v>17837</v>
+      </c>
+      <c r="C103" t="str">
+        <v>Муллабаев.С</v>
+      </c>
+      <c r="D103" t="str">
+        <v>Шаймердинова</v>
+      </c>
+      <c r="E103" t="str">
+        <v>69</v>
+      </c>
+      <c r="F103" t="str">
+        <v>77621</v>
+      </c>
+      <c r="G103" t="str">
+        <v>295</v>
+      </c>
+      <c r="H103" t="str">
+        <v>402</v>
+      </c>
+      <c r="I103" t="str">
+        <v>107</v>
+      </c>
+      <c r="J103" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K103" t="str">
+        <v>9</v>
+      </c>
+      <c r="L103" t="str">
+        <v>12</v>
+      </c>
+      <c r="M103" t="str">
+        <v>15</v>
+      </c>
+      <c r="N103" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B104" t="str">
+        <v>42209</v>
+      </c>
+      <c r="C104" t="str">
+        <v>Абубакирова Арзу</v>
+      </c>
+      <c r="D104" t="str">
+        <v>Бимурзаева</v>
+      </c>
+      <c r="E104" t="str">
+        <v>10</v>
+      </c>
+      <c r="F104" t="str">
+        <v>83079</v>
+      </c>
+      <c r="G104" t="str">
+        <v>1</v>
+      </c>
+      <c r="H104" t="str">
+        <v>220</v>
+      </c>
+      <c r="I104" t="str">
+        <v>219</v>
+      </c>
+      <c r="J104" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K104" t="str">
+        <v>9</v>
+      </c>
+      <c r="L104" t="str">
+        <v>13</v>
+      </c>
+      <c r="M104" t="str">
+        <v>9</v>
+      </c>
+      <c r="N104" t="str">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B105" t="str">
+        <v>28869</v>
+      </c>
+      <c r="C105" t="str">
+        <v>Кульбаев Г</v>
+      </c>
+      <c r="D105" t="str">
+        <v>Шахабиддина</v>
+      </c>
+      <c r="E105" t="str">
+        <v>120 а</v>
+      </c>
+      <c r="F105" t="str">
+        <v>78987</v>
+      </c>
+      <c r="G105" t="str">
+        <v>463</v>
+      </c>
+      <c r="H105" t="str">
+        <v>650</v>
+      </c>
+      <c r="I105" t="str">
+        <v>187</v>
+      </c>
+      <c r="J105" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K105" t="str">
+        <v>9</v>
+      </c>
+      <c r="L105" t="str">
+        <v>13</v>
+      </c>
+      <c r="M105" t="str">
+        <v>11</v>
+      </c>
+      <c r="N105" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B106" t="str">
+        <v>6044</v>
+      </c>
+      <c r="C106" t="str">
+        <v>Туребаев Мырзабай</v>
+      </c>
+      <c r="D106" t="str">
+        <v>Муса Жалиля(ПМК)</v>
+      </c>
+      <c r="E106" t="str">
+        <v>145</v>
+      </c>
+      <c r="F106" t="str">
+        <v>54413</v>
+      </c>
+      <c r="G106" t="str">
+        <v>1286</v>
+      </c>
+      <c r="H106" t="str">
+        <v>1310</v>
+      </c>
+      <c r="I106" t="str">
+        <v>24</v>
+      </c>
+      <c r="J106" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K106" t="str">
+        <v>9</v>
+      </c>
+      <c r="L106" t="str">
+        <v>13</v>
+      </c>
+      <c r="M106" t="str">
+        <v>11</v>
+      </c>
+      <c r="N106" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B107" t="str">
+        <v>26957</v>
+      </c>
+      <c r="C107" t="str">
+        <v>ТОО Гидрокурылыс</v>
+      </c>
+      <c r="D107" t="str">
+        <v>Чкалова</v>
+      </c>
+      <c r="E107" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F107" t="str">
+        <v>83921</v>
+      </c>
+      <c r="G107" t="str">
+        <v>1</v>
+      </c>
+      <c r="H107" t="str">
+        <v>300</v>
+      </c>
+      <c r="I107" t="str">
+        <v>299</v>
+      </c>
+      <c r="J107" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K107" t="str">
+        <v>9</v>
+      </c>
+      <c r="L107" t="str">
+        <v>18</v>
+      </c>
+      <c r="M107" t="str">
+        <v>13</v>
+      </c>
+      <c r="N107" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B108" t="str">
+        <v>2477</v>
+      </c>
+      <c r="C108" t="str">
+        <v>ИП Мустафаев</v>
+      </c>
+      <c r="D108" t="str">
+        <v>Аэродромная 69</v>
+      </c>
+      <c r="E108" t="str">
+        <v>18</v>
+      </c>
+      <c r="F108" t="str">
+        <v>54585</v>
+      </c>
+      <c r="G108" t="str">
+        <v>264</v>
+      </c>
+      <c r="H108" t="str">
+        <v>307</v>
+      </c>
+      <c r="I108" t="str">
+        <v>43</v>
+      </c>
+      <c r="J108" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K108" t="str">
+        <v>9</v>
+      </c>
+      <c r="L108" t="str">
+        <v>18</v>
+      </c>
+      <c r="M108" t="str">
+        <v>13</v>
+      </c>
+      <c r="N108" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B109" t="str">
+        <v>40409</v>
+      </c>
+      <c r="C109" t="str">
+        <v>Ип Джумашов Абдивали</v>
+      </c>
+      <c r="D109" t="str">
+        <v>Караб.шоссе</v>
+      </c>
+      <c r="E109" t="str">
+        <v>150а</v>
+      </c>
+      <c r="F109" t="str">
+        <v>73266</v>
+      </c>
+      <c r="G109" t="str">
+        <v>219</v>
+      </c>
+      <c r="H109" t="str">
+        <v>263</v>
+      </c>
+      <c r="I109" t="str">
+        <v>44</v>
+      </c>
+      <c r="J109" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K109" t="str">
+        <v>9</v>
+      </c>
+      <c r="L109" t="str">
+        <v>18</v>
+      </c>
+      <c r="M109" t="str">
+        <v>13</v>
+      </c>
+      <c r="N109" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B110" t="str">
+        <v>41369</v>
+      </c>
+      <c r="C110" t="str">
+        <v>Ип Омаров Ж</v>
+      </c>
+      <c r="D110" t="str">
+        <v>Караб.шоссе</v>
+      </c>
+      <c r="E110" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F110" t="str">
+        <v>79214</v>
+      </c>
+      <c r="G110" t="str">
+        <v>126</v>
+      </c>
+      <c r="H110" t="str">
+        <v>131</v>
+      </c>
+      <c r="I110" t="str">
+        <v>5</v>
+      </c>
+      <c r="J110" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K110" t="str">
+        <v>9</v>
+      </c>
+      <c r="L110" t="str">
+        <v>18</v>
+      </c>
+      <c r="M110" t="str">
+        <v>13</v>
+      </c>
+      <c r="N110" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B111" t="str">
+        <v>39526</v>
+      </c>
+      <c r="C111" t="str">
+        <v>ИП Абдиганиева</v>
+      </c>
+      <c r="D111" t="str">
+        <v>Караб.шоссе</v>
+      </c>
+      <c r="E111" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F111" t="str">
+        <v>68440</v>
+      </c>
+      <c r="G111" t="str">
+        <v>655</v>
+      </c>
+      <c r="H111" t="str">
+        <v>712</v>
+      </c>
+      <c r="I111" t="str">
+        <v>57</v>
+      </c>
+      <c r="J111" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K111" t="str">
+        <v>9</v>
+      </c>
+      <c r="L111" t="str">
+        <v>18</v>
+      </c>
+      <c r="M111" t="str">
+        <v>13</v>
+      </c>
+      <c r="N111" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B112" t="str">
+        <v>32653</v>
+      </c>
+      <c r="C112" t="str">
+        <v>Юг Мед</v>
+      </c>
+      <c r="D112" t="str">
+        <v>Караб.шоссе</v>
+      </c>
+      <c r="E112" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F112" t="str">
+        <v>62649</v>
+      </c>
+      <c r="G112" t="str">
+        <v>547</v>
+      </c>
+      <c r="H112" t="str">
+        <v>568</v>
+      </c>
+      <c r="I112" t="str">
+        <v>21</v>
+      </c>
+      <c r="J112" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K112" t="str">
+        <v>9</v>
+      </c>
+      <c r="L112" t="str">
+        <v>18</v>
+      </c>
+      <c r="M112" t="str">
+        <v>13</v>
+      </c>
+      <c r="N112" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B113" t="str">
+        <v>23916</v>
+      </c>
+      <c r="C113" t="str">
+        <v>ИП Турашбеков</v>
+      </c>
+      <c r="D113" t="str">
+        <v>Караб.шоссе</v>
+      </c>
+      <c r="E113" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F113" t="str">
+        <v>55869</v>
+      </c>
+      <c r="G113" t="str">
+        <v>1600</v>
+      </c>
+      <c r="H113" t="str">
+        <v>1708</v>
+      </c>
+      <c r="I113" t="str">
+        <v>108</v>
+      </c>
+      <c r="J113" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K113" t="str">
+        <v>9</v>
+      </c>
+      <c r="L113" t="str">
+        <v>18</v>
+      </c>
+      <c r="M113" t="str">
+        <v>13</v>
+      </c>
+      <c r="N113" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B114" t="str">
+        <v>22645</v>
+      </c>
+      <c r="C114" t="str">
+        <v>Кафе "Султан"</v>
+      </c>
+      <c r="D114" t="str">
+        <v>Караб.шоссе</v>
+      </c>
+      <c r="E114" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F114" t="str">
+        <v>80515</v>
+      </c>
+      <c r="G114" t="str">
+        <v>220</v>
+      </c>
+      <c r="H114" t="str">
+        <v>231</v>
+      </c>
+      <c r="I114" t="str">
+        <v>11</v>
+      </c>
+      <c r="J114" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K114" t="str">
+        <v>9</v>
+      </c>
+      <c r="L114" t="str">
+        <v>18</v>
+      </c>
+      <c r="M114" t="str">
+        <v>13</v>
+      </c>
+      <c r="N114" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B115" t="str">
+        <v>33847</v>
+      </c>
+      <c r="C115" t="str">
+        <v>ИП Исаков</v>
+      </c>
+      <c r="D115" t="str">
+        <v>Караб.шоссе</v>
+      </c>
+      <c r="E115" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F115" t="str">
+        <v>48674</v>
+      </c>
+      <c r="G115" t="str">
+        <v>2880</v>
+      </c>
+      <c r="H115" t="str">
+        <v>2966</v>
+      </c>
+      <c r="I115" t="str">
+        <v>86</v>
+      </c>
+      <c r="J115" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K115" t="str">
+        <v>9</v>
+      </c>
+      <c r="L115" t="str">
+        <v>18</v>
+      </c>
+      <c r="M115" t="str">
+        <v>13</v>
+      </c>
+      <c r="N115" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B116" t="str">
+        <v>26980</v>
+      </c>
+      <c r="C116" t="str">
+        <v xml:space="preserve"> Сто Рыскулов</v>
+      </c>
+      <c r="D116" t="str">
+        <v>Караб.шоссе</v>
+      </c>
+      <c r="E116" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F116" t="str">
+        <v>50123</v>
+      </c>
+      <c r="G116" t="str">
+        <v>1129</v>
+      </c>
+      <c r="H116" t="str">
+        <v>1155</v>
+      </c>
+      <c r="I116" t="str">
+        <v>26</v>
+      </c>
+      <c r="J116" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K116" t="str">
+        <v>9</v>
+      </c>
+      <c r="L116" t="str">
+        <v>18</v>
+      </c>
+      <c r="M116" t="str">
+        <v>13</v>
+      </c>
+      <c r="N116" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B117" t="str">
+        <v>33498</v>
+      </c>
+      <c r="C117" t="str">
+        <v>Иристаева Насиба</v>
+      </c>
+      <c r="D117" t="str">
+        <v>Караб.шоссе</v>
+      </c>
+      <c r="E117" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F117" t="str">
+        <v>47759</v>
+      </c>
+      <c r="G117" t="str">
+        <v>232</v>
+      </c>
+      <c r="H117" t="str">
+        <v>289</v>
+      </c>
+      <c r="I117" t="str">
+        <v>57</v>
+      </c>
+      <c r="J117" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K117" t="str">
+        <v>9</v>
+      </c>
+      <c r="L117" t="str">
+        <v>18</v>
+      </c>
+      <c r="M117" t="str">
+        <v>13</v>
+      </c>
+      <c r="N117" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B118" t="str">
+        <v>7044</v>
+      </c>
+      <c r="C118" t="str">
+        <v>ИП Юлимов Ш,Ж</v>
+      </c>
+      <c r="D118" t="str">
+        <v>Организация</v>
+      </c>
+      <c r="E118" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F118" t="str">
+        <v>60486</v>
+      </c>
+      <c r="G118" t="str">
+        <v>1920</v>
+      </c>
+      <c r="H118" t="str">
+        <v>1937</v>
+      </c>
+      <c r="I118" t="str">
+        <v>17</v>
+      </c>
+      <c r="J118" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K118" t="str">
+        <v>9</v>
+      </c>
+      <c r="L118" t="str">
+        <v>18</v>
+      </c>
+      <c r="M118" t="str">
+        <v>13</v>
+      </c>
+      <c r="N118" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B119" t="str">
+        <v>38290</v>
+      </c>
+      <c r="C119" t="str">
+        <v>МОЙКА 24</v>
+      </c>
+      <c r="D119" t="str">
+        <v>Организация</v>
+      </c>
+      <c r="E119" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F119" t="str">
+        <v>81248</v>
+      </c>
+      <c r="G119" t="str">
+        <v>791</v>
+      </c>
+      <c r="H119" t="str">
+        <v>950</v>
+      </c>
+      <c r="I119" t="str">
+        <v>159</v>
+      </c>
+      <c r="J119" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K119" t="str">
+        <v>9</v>
+      </c>
+      <c r="L119" t="str">
+        <v>18</v>
+      </c>
+      <c r="M119" t="str">
+        <v>13</v>
+      </c>
+      <c r="N119" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B120" t="str">
+        <v>23392</v>
+      </c>
+      <c r="C120" t="str">
+        <v>Мойка АКСУ</v>
+      </c>
+      <c r="D120" t="str">
+        <v>Организация</v>
+      </c>
+      <c r="E120" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F120" t="str">
+        <v>81621</v>
+      </c>
+      <c r="G120" t="str">
+        <v>659</v>
+      </c>
+      <c r="H120" t="str">
+        <v>751</v>
+      </c>
+      <c r="I120" t="str">
+        <v>92</v>
+      </c>
+      <c r="J120" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K120" t="str">
+        <v>9</v>
+      </c>
+      <c r="L120" t="str">
+        <v>18</v>
+      </c>
+      <c r="M120" t="str">
+        <v>13</v>
+      </c>
+      <c r="N120" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B121" t="str">
+        <v>2443</v>
+      </c>
+      <c r="C121" t="str">
+        <v>Маг "Юмакс"</v>
+      </c>
+      <c r="D121" t="str">
+        <v>Организация</v>
+      </c>
+      <c r="E121" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F121" t="str">
+        <v>55276</v>
+      </c>
+      <c r="G121" t="str">
+        <v>318</v>
+      </c>
+      <c r="H121" t="str">
+        <v>336</v>
+      </c>
+      <c r="I121" t="str">
+        <v>18</v>
+      </c>
+      <c r="J121" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K121" t="str">
+        <v>9</v>
+      </c>
+      <c r="L121" t="str">
+        <v>18</v>
+      </c>
+      <c r="M121" t="str">
+        <v>13</v>
+      </c>
+      <c r="N121" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B122" t="str">
+        <v>2451</v>
+      </c>
+      <c r="C122" t="str">
+        <v>ИП "Худайбергенов"</v>
+      </c>
+      <c r="D122" t="str">
+        <v>Организация</v>
+      </c>
+      <c r="E122" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F122" t="str">
+        <v>76301</v>
+      </c>
+      <c r="G122" t="str">
+        <v>1702</v>
+      </c>
+      <c r="H122" t="str">
+        <v>1812</v>
+      </c>
+      <c r="I122" t="str">
+        <v>110</v>
+      </c>
+      <c r="J122" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K122" t="str">
+        <v>9</v>
+      </c>
+      <c r="L122" t="str">
+        <v>18</v>
+      </c>
+      <c r="M122" t="str">
+        <v>13</v>
+      </c>
+      <c r="N122" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B123" t="str">
+        <v>2452</v>
+      </c>
+      <c r="C123" t="str">
+        <v>Маг "Ак Ниет"</v>
+      </c>
+      <c r="D123" t="str">
+        <v>Организация</v>
+      </c>
+      <c r="E123" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F123" t="str">
+        <v>50378</v>
+      </c>
+      <c r="G123" t="str">
+        <v>1947</v>
+      </c>
+      <c r="H123" t="str">
+        <v>1977</v>
+      </c>
+      <c r="I123" t="str">
+        <v>30</v>
+      </c>
+      <c r="J123" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K123" t="str">
+        <v>9</v>
+      </c>
+      <c r="L123" t="str">
+        <v>18</v>
+      </c>
+      <c r="M123" t="str">
+        <v>13</v>
+      </c>
+      <c r="N123" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B124" t="str">
+        <v>2455</v>
+      </c>
+      <c r="C124" t="str">
+        <v>Маг "Береке"</v>
+      </c>
+      <c r="D124" t="str">
+        <v>Организация</v>
+      </c>
+      <c r="E124" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F124" t="str">
+        <v>64485</v>
+      </c>
+      <c r="G124" t="str">
+        <v>79</v>
+      </c>
+      <c r="H124" t="str">
+        <v>124</v>
+      </c>
+      <c r="I124" t="str">
+        <v>45</v>
+      </c>
+      <c r="J124" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K124" t="str">
+        <v>9</v>
+      </c>
+      <c r="L124" t="str">
+        <v>18</v>
+      </c>
+      <c r="M124" t="str">
+        <v>13</v>
+      </c>
+      <c r="N124" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B125" t="str">
+        <v>2457</v>
+      </c>
+      <c r="C125" t="str">
+        <v>Сембекова Д</v>
+      </c>
+      <c r="D125" t="str">
+        <v>Организация</v>
+      </c>
+      <c r="E125" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F125" t="str">
+        <v>81560</v>
+      </c>
+      <c r="G125" t="str">
+        <v>43</v>
+      </c>
+      <c r="H125" t="str">
+        <v>52</v>
+      </c>
+      <c r="I125" t="str">
+        <v>9</v>
+      </c>
+      <c r="J125" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K125" t="str">
+        <v>9</v>
+      </c>
+      <c r="L125" t="str">
+        <v>18</v>
+      </c>
+      <c r="M125" t="str">
+        <v>13</v>
+      </c>
+      <c r="N125" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B126" t="str">
+        <v>41780</v>
+      </c>
+      <c r="C126" t="str">
+        <v>Ип Койлыбеков Д</v>
+      </c>
+      <c r="D126" t="str">
+        <v>Сейфуллина</v>
+      </c>
+      <c r="E126" t="str">
+        <v>65б</v>
+      </c>
+      <c r="F126" t="str">
+        <v>81204</v>
+      </c>
+      <c r="G126" t="str">
+        <v>12</v>
+      </c>
+      <c r="H126" t="str">
+        <v>25</v>
+      </c>
+      <c r="I126" t="str">
+        <v>13</v>
+      </c>
+      <c r="J126" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K126" t="str">
+        <v>9</v>
+      </c>
+      <c r="L126" t="str">
+        <v>18</v>
+      </c>
+      <c r="M126" t="str">
+        <v>13</v>
+      </c>
+      <c r="N126" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B127" t="str">
+        <v>41555</v>
+      </c>
+      <c r="C127" t="str">
+        <v>Жанар Салон Мухлиса</v>
+      </c>
+      <c r="D127" t="str">
+        <v>Сураншы Батыра</v>
+      </c>
+      <c r="E127" t="str">
+        <v>115м</v>
+      </c>
+      <c r="F127" t="str">
+        <v>80027</v>
+      </c>
+      <c r="G127" t="str">
+        <v>13</v>
+      </c>
+      <c r="H127" t="str">
+        <v>24</v>
+      </c>
+      <c r="I127" t="str">
+        <v>11</v>
+      </c>
+      <c r="J127" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K127" t="str">
+        <v>9</v>
+      </c>
+      <c r="L127" t="str">
+        <v>18</v>
+      </c>
+      <c r="M127" t="str">
+        <v>13</v>
+      </c>
+      <c r="N127" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B128" t="str">
+        <v>41553</v>
+      </c>
+      <c r="C128" t="str">
+        <v>Ип Жанар Мурской Сал</v>
+      </c>
+      <c r="D128" t="str">
+        <v>Сураншы Батыра</v>
+      </c>
+      <c r="E128" t="str">
+        <v>115б</v>
+      </c>
+      <c r="F128" t="str">
+        <v>80025</v>
+      </c>
+      <c r="G128" t="str">
+        <v>48</v>
+      </c>
+      <c r="H128" t="str">
+        <v>56</v>
+      </c>
+      <c r="I128" t="str">
+        <v>8</v>
+      </c>
+      <c r="J128" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K128" t="str">
+        <v>9</v>
+      </c>
+      <c r="L128" t="str">
+        <v>18</v>
+      </c>
+      <c r="M128" t="str">
+        <v>13</v>
+      </c>
+      <c r="N128" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B129" t="str">
+        <v>1904</v>
+      </c>
+      <c r="C129" t="str">
+        <v>Ип Ниязбекова</v>
+      </c>
+      <c r="D129" t="str">
+        <v>Сураншы Батыра</v>
+      </c>
+      <c r="E129" t="str">
+        <v>2</v>
+      </c>
+      <c r="F129" t="str">
+        <v>77365</v>
+      </c>
+      <c r="G129" t="str">
+        <v>155</v>
+      </c>
+      <c r="H129" t="str">
+        <v>179</v>
+      </c>
+      <c r="I129" t="str">
+        <v>24</v>
+      </c>
+      <c r="J129" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K129" t="str">
+        <v>9</v>
+      </c>
+      <c r="L129" t="str">
+        <v>18</v>
+      </c>
+      <c r="M129" t="str">
+        <v>13</v>
+      </c>
+      <c r="N129" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B130" t="str">
+        <v>1934</v>
+      </c>
+      <c r="C130" t="str">
+        <v>Ип Ниязбекова</v>
+      </c>
+      <c r="D130" t="str">
+        <v>Сураншы Батыра</v>
+      </c>
+      <c r="E130" t="str">
+        <v>31</v>
+      </c>
+      <c r="F130" t="str">
+        <v>76916</v>
+      </c>
+      <c r="G130" t="str">
+        <v>952</v>
+      </c>
+      <c r="H130" t="str">
+        <v>978</v>
+      </c>
+      <c r="I130" t="str">
+        <v>26</v>
+      </c>
+      <c r="J130" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K130" t="str">
+        <v>9</v>
+      </c>
+      <c r="L130" t="str">
+        <v>18</v>
+      </c>
+      <c r="M130" t="str">
+        <v>13</v>
+      </c>
+      <c r="N130" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B131" t="str">
+        <v>35406</v>
+      </c>
+      <c r="C131" t="str">
+        <v>ИП Тохтарова</v>
+      </c>
+      <c r="D131" t="str">
+        <v>Сураншы Батыра</v>
+      </c>
+      <c r="E131" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F131" t="str">
+        <v>55249</v>
+      </c>
+      <c r="G131" t="str">
+        <v>298</v>
+      </c>
+      <c r="H131" t="str">
+        <v>344</v>
+      </c>
+      <c r="I131" t="str">
+        <v>46</v>
+      </c>
+      <c r="J131" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K131" t="str">
+        <v>9</v>
+      </c>
+      <c r="L131" t="str">
+        <v>18</v>
+      </c>
+      <c r="M131" t="str">
+        <v>13</v>
+      </c>
+      <c r="N131" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B132" t="str">
+        <v>13274</v>
+      </c>
+      <c r="C132" t="str">
+        <v>Мойка Бек арыс</v>
+      </c>
+      <c r="D132" t="str">
+        <v>Сураншы Батыра</v>
+      </c>
+      <c r="E132" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F132" t="str">
+        <v>83928</v>
+      </c>
+      <c r="G132" t="str">
+        <v>1</v>
+      </c>
+      <c r="H132" t="str">
+        <v>750</v>
+      </c>
+      <c r="I132" t="str">
+        <v>749</v>
+      </c>
+      <c r="J132" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K132" t="str">
+        <v>9</v>
+      </c>
+      <c r="L132" t="str">
+        <v>18</v>
+      </c>
+      <c r="M132" t="str">
+        <v>13</v>
+      </c>
+      <c r="N132" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B133" t="str">
+        <v>40817</v>
+      </c>
+      <c r="C133" t="str">
+        <v>Маг Авто Запчасти</v>
+      </c>
+      <c r="D133" t="str">
+        <v>Сураншы Батыра</v>
+      </c>
+      <c r="E133" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F133" t="str">
+        <v>75507</v>
+      </c>
+      <c r="G133" t="str">
+        <v>209</v>
+      </c>
+      <c r="H133" t="str">
+        <v>241</v>
+      </c>
+      <c r="I133" t="str">
+        <v>32</v>
+      </c>
+      <c r="J133" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K133" t="str">
+        <v>9</v>
+      </c>
+      <c r="L133" t="str">
+        <v>18</v>
+      </c>
+      <c r="M133" t="str">
+        <v>13</v>
+      </c>
+      <c r="N133" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B134" t="str">
+        <v>17634</v>
+      </c>
+      <c r="C134" t="str">
+        <v>Ясли сад Кайнар</v>
+      </c>
+      <c r="D134" t="str">
+        <v>Чкалова</v>
+      </c>
+      <c r="E134" t="str">
+        <v>19.</v>
+      </c>
+      <c r="F134" t="str">
+        <v>73687</v>
+      </c>
+      <c r="G134" t="str">
+        <v>1728</v>
+      </c>
+      <c r="H134" t="str">
+        <v>1860</v>
+      </c>
+      <c r="I134" t="str">
+        <v>132</v>
+      </c>
+      <c r="J134" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K134" t="str">
+        <v>9</v>
+      </c>
+      <c r="L134" t="str">
+        <v>18</v>
+      </c>
+      <c r="M134" t="str">
+        <v>13</v>
+      </c>
+      <c r="N134" t="str">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B135" t="str">
+        <v>35477</v>
+      </c>
+      <c r="C135" t="str">
+        <v>Ип Али Даряб</v>
+      </c>
+      <c r="D135" t="str">
+        <v>Чкалова</v>
+      </c>
+      <c r="E135" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F135" t="str">
+        <v>81883</v>
+      </c>
+      <c r="G135" t="str">
+        <v>100</v>
+      </c>
+      <c r="H135" t="str">
+        <v>115</v>
+      </c>
+      <c r="I135" t="str">
+        <v>15</v>
+      </c>
+      <c r="J135" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K135" t="str">
+        <v>9</v>
+      </c>
+      <c r="L135" t="str">
+        <v>18</v>
+      </c>
+      <c r="M135" t="str">
+        <v>13</v>
+      </c>
+      <c r="N135" t="str">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B136" t="str">
+        <v>38545</v>
+      </c>
+      <c r="C136" t="str">
+        <v>Шанбай Бакытжан</v>
+      </c>
+      <c r="D136" t="str">
+        <v>Чкалова</v>
+      </c>
+      <c r="E136" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F136" t="str">
+        <v>63569</v>
+      </c>
+      <c r="G136" t="str">
+        <v>462</v>
+      </c>
+      <c r="H136" t="str">
+        <v>492</v>
+      </c>
+      <c r="I136" t="str">
+        <v>30</v>
+      </c>
+      <c r="J136" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K136" t="str">
+        <v>9</v>
+      </c>
+      <c r="L136" t="str">
+        <v>18</v>
+      </c>
+      <c r="M136" t="str">
+        <v>13</v>
+      </c>
+      <c r="N136" t="str">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B137" t="str">
+        <v>39051</v>
+      </c>
+      <c r="C137" t="str">
+        <v>ИП Баратов Б</v>
+      </c>
+      <c r="D137" t="str">
+        <v>Шахабиддина</v>
+      </c>
+      <c r="E137" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F137" t="str">
+        <v>65249</v>
+      </c>
+      <c r="G137" t="str">
+        <v>207</v>
+      </c>
+      <c r="H137" t="str">
+        <v>259</v>
+      </c>
+      <c r="I137" t="str">
+        <v>52</v>
+      </c>
+      <c r="J137" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K137" t="str">
+        <v>9</v>
+      </c>
+      <c r="L137" t="str">
+        <v>18</v>
+      </c>
+      <c r="M137" t="str">
+        <v>13</v>
+      </c>
+      <c r="N137" t="str">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B138" t="str">
+        <v>1560</v>
+      </c>
+      <c r="C138" t="str">
+        <v>Мойка Кудабаев Серик</v>
+      </c>
+      <c r="D138" t="str">
+        <v>Шахабиддина</v>
+      </c>
+      <c r="E138" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F138" t="str">
+        <v>67542</v>
+      </c>
+      <c r="G138" t="str">
+        <v>318</v>
+      </c>
+      <c r="H138" t="str">
+        <v>332</v>
+      </c>
+      <c r="I138" t="str">
+        <v>14</v>
+      </c>
+      <c r="J138" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K138" t="str">
+        <v>9</v>
+      </c>
+      <c r="L138" t="str">
+        <v>18</v>
+      </c>
+      <c r="M138" t="str">
+        <v>13</v>
+      </c>
+      <c r="N138" t="str">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B139" t="str">
+        <v>38733</v>
+      </c>
+      <c r="C139" t="str">
+        <v>ИП Махкамов</v>
+      </c>
+      <c r="D139" t="str">
+        <v>Караб.шоссе</v>
+      </c>
+      <c r="E139" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F139" t="str">
+        <v>83925</v>
+      </c>
+      <c r="G139" t="str">
+        <v>1</v>
+      </c>
+      <c r="H139" t="str">
+        <v>80</v>
+      </c>
+      <c r="I139" t="str">
+        <v>79</v>
+      </c>
+      <c r="J139" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K139" t="str">
+        <v>9</v>
+      </c>
+      <c r="L139" t="str">
+        <v>19</v>
+      </c>
+      <c r="M139" t="str">
+        <v>11</v>
+      </c>
+      <c r="N139" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B140" t="str">
+        <v>1514</v>
+      </c>
+      <c r="C140" t="str">
+        <v>Балханбаев Мамадали</v>
+      </c>
+      <c r="D140" t="str">
+        <v>Сураншы Батыра 29</v>
+      </c>
+      <c r="E140" t="str">
+        <v>7</v>
+      </c>
+      <c r="F140" t="str">
+        <v>83909</v>
+      </c>
+      <c r="G140" t="str">
+        <v>1</v>
+      </c>
+      <c r="H140" t="str">
+        <v>63</v>
+      </c>
+      <c r="I140" t="str">
+        <v>62</v>
+      </c>
+      <c r="J140" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K140" t="str">
+        <v>9</v>
+      </c>
+      <c r="L140" t="str">
+        <v>19</v>
+      </c>
+      <c r="M140" t="str">
+        <v>20</v>
+      </c>
+      <c r="N140" t="str">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B141" t="str">
+        <v>35614</v>
+      </c>
+      <c r="C141" t="str">
+        <v>Шынгысбеков Сапарали</v>
+      </c>
+      <c r="D141" t="str">
+        <v>Абай (Кутарыс)</v>
+      </c>
+      <c r="E141" t="str">
+        <v>76</v>
+      </c>
+      <c r="F141" t="str">
+        <v>79514</v>
+      </c>
+      <c r="G141" t="str">
+        <v>625</v>
+      </c>
+      <c r="H141" t="str">
+        <v>840</v>
+      </c>
+      <c r="I141" t="str">
+        <v>215</v>
+      </c>
+      <c r="J141" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K141" t="str">
+        <v>9</v>
+      </c>
+      <c r="L141" t="str">
+        <v>20</v>
+      </c>
+      <c r="M141" t="str">
+        <v>11</v>
+      </c>
+      <c r="N141" t="str">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B142" t="str">
+        <v>2458</v>
+      </c>
+      <c r="C142" t="str">
+        <v>ТНП Бурбеков (Юсуф)</v>
+      </c>
+      <c r="D142" t="str">
+        <v>Организация</v>
+      </c>
+      <c r="E142" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F142" t="str">
+        <v>83900</v>
+      </c>
+      <c r="G142" t="str">
+        <v>1</v>
+      </c>
+      <c r="H142" t="str">
+        <v>80</v>
+      </c>
+      <c r="I142" t="str">
+        <v>79</v>
+      </c>
+      <c r="J142" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K142" t="str">
+        <v>9</v>
+      </c>
+      <c r="L142" t="str">
+        <v>22</v>
+      </c>
+      <c r="M142" t="str">
+        <v>8</v>
+      </c>
+      <c r="N142" t="str">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B143" t="str">
+        <v>36464</v>
+      </c>
+      <c r="C143" t="str">
+        <v>Юсупова Унсунай</v>
+      </c>
+      <c r="D143" t="str">
+        <v>А.Курбанова</v>
+      </c>
+      <c r="E143" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F143" t="str">
+        <v>58847</v>
+      </c>
+      <c r="G143" t="str">
+        <v>1125</v>
+      </c>
+      <c r="H143" t="str">
+        <v>1188</v>
+      </c>
+      <c r="I143" t="str">
+        <v>63</v>
+      </c>
+      <c r="J143" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K143" t="str">
+        <v>9</v>
+      </c>
+      <c r="L143" t="str">
+        <v>28</v>
+      </c>
+      <c r="M143" t="str">
+        <v>15</v>
+      </c>
+      <c r="N143" t="str">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B144" t="str">
+        <v>38093</v>
+      </c>
+      <c r="C144" t="str">
+        <v>Ибрагимжанов Рустам</v>
+      </c>
+      <c r="D144" t="str">
+        <v>А.Курбанова</v>
+      </c>
+      <c r="E144" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F144" t="str">
+        <v>61424</v>
+      </c>
+      <c r="G144" t="str">
+        <v>783</v>
+      </c>
+      <c r="H144" t="str">
+        <v>826</v>
+      </c>
+      <c r="I144" t="str">
+        <v>43</v>
+      </c>
+      <c r="J144" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K144" t="str">
+        <v>9</v>
+      </c>
+      <c r="L144" t="str">
+        <v>28</v>
+      </c>
+      <c r="M144" t="str">
+        <v>16</v>
+      </c>
+      <c r="N144" t="str">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B145" t="str">
+        <v>39009</v>
+      </c>
+      <c r="C145" t="str">
+        <v>Юлдашев Мирзадавлет</v>
+      </c>
+      <c r="D145" t="str">
+        <v>Курбенова</v>
+      </c>
+      <c r="E145" t="str">
+        <v>14/4</v>
+      </c>
+      <c r="F145" t="str">
+        <v>64851</v>
+      </c>
+      <c r="G145" t="str">
+        <v>707</v>
+      </c>
+      <c r="H145" t="str">
+        <v>790</v>
+      </c>
+      <c r="I145" t="str">
+        <v>83</v>
+      </c>
+      <c r="J145" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K145" t="str">
+        <v>9</v>
+      </c>
+      <c r="L145" t="str">
+        <v>28</v>
+      </c>
+      <c r="M145" t="str">
+        <v>16</v>
+      </c>
+      <c r="N145" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B146" t="str">
+        <v>35544</v>
+      </c>
+      <c r="C146" t="str">
+        <v>Курбантаев Муратжан</v>
+      </c>
+      <c r="D146" t="str">
+        <v>А.Курбанова</v>
+      </c>
+      <c r="E146" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F146" t="str">
+        <v>55659</v>
+      </c>
+      <c r="G146" t="str">
+        <v>425</v>
+      </c>
+      <c r="H146" t="str">
+        <v>442</v>
+      </c>
+      <c r="I146" t="str">
+        <v>17</v>
+      </c>
+      <c r="J146" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K146" t="str">
+        <v>9</v>
+      </c>
+      <c r="L146" t="str">
+        <v>28</v>
+      </c>
+      <c r="M146" t="str">
+        <v>16</v>
+      </c>
+      <c r="N146" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B147" t="str">
+        <v>17804</v>
+      </c>
+      <c r="C147" t="str">
+        <v>Эшполотов.Т</v>
+      </c>
+      <c r="D147" t="str">
+        <v>Шаймердинова</v>
+      </c>
+      <c r="E147" t="str">
+        <v>54</v>
+      </c>
+      <c r="F147" t="str">
+        <v>83904</v>
+      </c>
+      <c r="G147" t="str">
+        <v>1</v>
+      </c>
+      <c r="H147" t="str">
+        <v>128</v>
+      </c>
+      <c r="I147" t="str">
+        <v>127</v>
+      </c>
+      <c r="J147" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K147" t="str">
+        <v>9</v>
+      </c>
+      <c r="L147" t="str">
+        <v>28</v>
+      </c>
+      <c r="M147" t="str">
+        <v>16</v>
+      </c>
+      <c r="N147" t="str">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B148" t="str">
+        <v>17841</v>
+      </c>
+      <c r="C148" t="str">
+        <v>Исмаилов.Х</v>
+      </c>
+      <c r="D148" t="str">
+        <v>Шаймердинова</v>
+      </c>
+      <c r="E148" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F148" t="str">
+        <v>83845</v>
+      </c>
+      <c r="G148" t="str">
+        <v>1</v>
+      </c>
+      <c r="H148" t="str">
+        <v>111</v>
+      </c>
+      <c r="I148" t="str">
+        <v>110</v>
+      </c>
+      <c r="J148" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K148" t="str">
+        <v>9</v>
+      </c>
+      <c r="L148" t="str">
+        <v>28</v>
+      </c>
+      <c r="M148" t="str">
+        <v>16</v>
+      </c>
+      <c r="N148" t="str">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B149" t="str">
+        <v>16331</v>
+      </c>
+      <c r="C149" t="str">
+        <v>Сайдуллаева.Х</v>
+      </c>
+      <c r="D149" t="str">
+        <v>Желтоксан</v>
+      </c>
+      <c r="E149" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F149" t="str">
+        <v>46136</v>
+      </c>
+      <c r="G149" t="str">
+        <v>717</v>
+      </c>
+      <c r="H149" t="str">
+        <v>728</v>
+      </c>
+      <c r="I149" t="str">
+        <v>11</v>
+      </c>
+      <c r="J149" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K149" t="str">
+        <v>9</v>
+      </c>
+      <c r="L149" t="str">
+        <v>28</v>
+      </c>
+      <c r="M149" t="str">
+        <v>17</v>
+      </c>
+      <c r="N149" t="str">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B150" t="str">
+        <v>2064</v>
+      </c>
+      <c r="C150" t="str">
+        <v>Пономаренко</v>
+      </c>
+      <c r="D150" t="str">
+        <v>Калдаякова</v>
+      </c>
+      <c r="E150" t="str">
+        <v>114</v>
+      </c>
+      <c r="F150" t="str">
+        <v>77191</v>
+      </c>
+      <c r="G150" t="str">
+        <v>240</v>
+      </c>
+      <c r="H150" t="str">
+        <v>1390</v>
+      </c>
+      <c r="I150" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J150" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K150" t="str">
+        <v>9</v>
+      </c>
+      <c r="L150" t="str">
+        <v>29</v>
+      </c>
+      <c r="M150" t="str">
+        <v>9</v>
+      </c>
+      <c r="N150" t="str">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B151" t="str">
+        <v>36579</v>
+      </c>
+      <c r="C151" t="str">
+        <v>Эшанкулов Октам</v>
+      </c>
+      <c r="D151" t="str">
+        <v>Х.Ташева</v>
+      </c>
+      <c r="E151" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F151" t="str">
+        <v>83745</v>
+      </c>
+      <c r="G151" t="str">
+        <v>1</v>
+      </c>
+      <c r="H151" t="str">
+        <v>247</v>
+      </c>
+      <c r="I151" t="str">
+        <v>246</v>
+      </c>
+      <c r="J151" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K151" t="str">
+        <v>9</v>
+      </c>
+      <c r="L151" t="str">
+        <v>29</v>
+      </c>
+      <c r="M151" t="str">
+        <v>17</v>
+      </c>
+      <c r="N151" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B152" t="str">
+        <v>16072</v>
+      </c>
+      <c r="C152" t="str">
+        <v>Умирханова</v>
+      </c>
+      <c r="D152" t="str">
+        <v>Абдугаппарова</v>
+      </c>
+      <c r="E152" t="str">
+        <v>9</v>
+      </c>
+      <c r="F152" t="str">
+        <v>57559</v>
+      </c>
+      <c r="G152" t="str">
+        <v>1905</v>
+      </c>
+      <c r="H152" t="str">
+        <v>2122</v>
+      </c>
+      <c r="I152" t="str">
+        <v>217</v>
+      </c>
+      <c r="J152" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K152" t="str">
+        <v>10</v>
+      </c>
+      <c r="L152" t="str">
+        <v>1</v>
+      </c>
+      <c r="M152" t="str">
+        <v>11</v>
+      </c>
+      <c r="N152" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B153" t="str">
+        <v>36915</v>
+      </c>
+      <c r="C153" t="str">
+        <v>д/с Кыз бала</v>
+      </c>
+      <c r="D153" t="str">
+        <v>Шертаев (Ширкин)</v>
+      </c>
+      <c r="E153" t="str">
+        <v>26</v>
+      </c>
+      <c r="F153" t="str">
+        <v>77839</v>
+      </c>
+      <c r="G153" t="str">
+        <v>1010</v>
+      </c>
+      <c r="H153" t="str">
+        <v>1080</v>
+      </c>
+      <c r="I153" t="str">
+        <v>70</v>
+      </c>
+      <c r="J153" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K153" t="str">
+        <v>10</v>
+      </c>
+      <c r="L153" t="str">
+        <v>3</v>
+      </c>
+      <c r="M153" t="str">
+        <v>16</v>
+      </c>
+      <c r="N153" t="str">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B154" t="str">
+        <v>28741</v>
+      </c>
+      <c r="C154" t="str">
+        <v>ИП Джимбаев Б.Ж</v>
+      </c>
+      <c r="D154" t="str">
+        <v>Шаймердинова</v>
+      </c>
+      <c r="E154" t="str">
+        <v>3</v>
+      </c>
+      <c r="F154" t="str">
+        <v>77747</v>
+      </c>
+      <c r="G154" t="str">
+        <v>5564</v>
+      </c>
+      <c r="H154" t="str">
+        <v>5785</v>
+      </c>
+      <c r="I154" t="str">
+        <v>221</v>
+      </c>
+      <c r="J154" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K154" t="str">
+        <v>10</v>
+      </c>
+      <c r="L154" t="str">
+        <v>28</v>
+      </c>
+      <c r="M154" t="str">
+        <v>14</v>
+      </c>
+      <c r="N154" t="str">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B155" t="str">
+        <v>41553</v>
+      </c>
+      <c r="C155" t="str">
+        <v>Ип Жанар Мурской Сал</v>
+      </c>
+      <c r="D155" t="str">
+        <v>Сураншы Батыра</v>
+      </c>
+      <c r="E155" t="str">
+        <v>115б</v>
+      </c>
+      <c r="F155" t="str">
+        <v>80025</v>
+      </c>
+      <c r="G155" t="str">
+        <v>56</v>
+      </c>
+      <c r="H155" t="str">
+        <v>65</v>
+      </c>
+      <c r="I155" t="str">
+        <v>9</v>
+      </c>
+      <c r="J155" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K155" t="str">
+        <v>11</v>
+      </c>
+      <c r="L155" t="str">
+        <v>27</v>
+      </c>
+      <c r="M155" t="str">
+        <v>13</v>
+      </c>
+      <c r="N155" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B156" t="str">
+        <v>1628</v>
+      </c>
+      <c r="C156" t="str">
+        <v>Чалова</v>
+      </c>
+      <c r="D156" t="str">
+        <v>Сураншы Батыра 36</v>
+      </c>
+      <c r="E156" t="str">
+        <v>31</v>
+      </c>
+      <c r="F156" t="str">
+        <v>55873</v>
+      </c>
+      <c r="G156" t="str">
+        <v>213</v>
+      </c>
+      <c r="H156" t="str">
+        <v>216</v>
+      </c>
+      <c r="I156" t="str">
+        <v>3</v>
+      </c>
+      <c r="J156" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K156" t="str">
+        <v>11</v>
+      </c>
+      <c r="L156" t="str">
+        <v>27</v>
+      </c>
+      <c r="M156" t="str">
+        <v>13</v>
+      </c>
+      <c r="N156" t="str">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B157" t="str">
+        <v>23336</v>
+      </c>
+      <c r="C157" t="str">
+        <v>Самал кафе</v>
+      </c>
+      <c r="D157" t="str">
+        <v>Караб.шоссе</v>
+      </c>
+      <c r="E157" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F157" t="str">
+        <v>50515</v>
+      </c>
+      <c r="G157" t="str">
+        <v>1479</v>
+      </c>
+      <c r="H157" t="str">
+        <v>1536</v>
+      </c>
+      <c r="I157" t="str">
+        <v>57</v>
+      </c>
+      <c r="J157" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K157" t="str">
+        <v>11</v>
+      </c>
+      <c r="L157" t="str">
+        <v>27</v>
+      </c>
+      <c r="M157" t="str">
+        <v>13</v>
+      </c>
+      <c r="N157" t="str">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>Ревизор - Жамшид</v>
+      </c>
+      <c r="B158" t="str">
+        <v>19991</v>
+      </c>
+      <c r="C158" t="str">
+        <v>Анаркулов Хуршид</v>
+      </c>
+      <c r="D158" t="str">
+        <v>Сайрамская</v>
+      </c>
+      <c r="E158" t="str">
+        <v>6</v>
+      </c>
+      <c r="F158" t="str">
+        <v>65102</v>
+      </c>
+      <c r="G158" t="str">
+        <v>2088</v>
+      </c>
+      <c r="H158" t="str">
+        <v>3468</v>
+      </c>
+      <c r="I158" t="str">
+        <v>1380</v>
+      </c>
+      <c r="J158" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K158" t="str">
+        <v>11</v>
+      </c>
+      <c r="L158" t="str">
+        <v>28</v>
+      </c>
+      <c r="M158" t="str">
+        <v>14</v>
+      </c>
+      <c r="N158" t="str">
+        <v>51</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:N43"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N78"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N158"/>
   </ignoredErrors>
 </worksheet>
 </file>